--- a/data/rme_pcr-score.xlsx
+++ b/data/rme_pcr-score.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucc-my.sharepoint.com/personal/chris_bird_tamucc_edu/Documents/!students/Labrador_Dissertation/09_github-repositories/kll_chapter2_edna-optimization/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucc-my.sharepoint.com/personal/chris_bird_tamucc_edu/Documents/!students/Labrador_Dissertation/09_github-repositories/2026_labrador_preservation-of-edna-from-remote-areas/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="284" documentId="11_F25DC773A252ABDACC104819619D540C5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F0F6334-7830-4D8B-8C39-DF749C9FD7FB}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="1710" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
